--- a/templates/order_template.xlsx
+++ b/templates/order_template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/parrottkim/Projects/javascript/taskflow-backend/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3E7E2D1-222A-3C4C-B48C-C636E236E839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6B98D9-1953-C14C-98EC-5D14BCD5DD7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>발   주   서</t>
   </si>
@@ -80,9 +80,6 @@
   <si>
     <t>서울 금천구 가산디지털1로 168 (가산동)
 우림라이온스밸리 C동 12층 1210호</t>
-  </si>
-  <si>
-    <t>FAX</t>
   </si>
   <si>
     <t>구  매  담  당  /  연  락  처</t>
@@ -149,6 +146,14 @@
   </si>
   <si>
     <t>특  기  사  항</t>
+  </si>
+  <si>
+    <t>제목</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>제            목</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -417,71 +422,71 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -951,647 +956,741 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="140" customHeight="1">
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
     </row>
     <row r="4" spans="1:14" ht="61">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
     </row>
     <row r="6" spans="1:14" ht="30" customHeight="1">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="13" t="s">
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
     </row>
     <row r="7" spans="1:14" ht="30" customHeight="1">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13" t="s">
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
     </row>
     <row r="8" spans="1:14" ht="30" customHeight="1">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="12" t="s">
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="J8" s="13" t="s">
+      <c r="I8" s="27"/>
+      <c r="J8" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
     </row>
     <row r="9" spans="1:14" ht="30" customHeight="1">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="13" t="s">
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="12" t="s">
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="12"/>
-      <c r="J9" s="13" t="s">
+      <c r="I9" s="27"/>
+      <c r="J9" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
     </row>
     <row r="10" spans="1:14" ht="30" customHeight="1">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="13" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="12" t="s">
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="15" t="s">
+      <c r="I10" s="27"/>
+      <c r="J10" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="15"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
     </row>
     <row r="11" spans="1:14" ht="30" customHeight="1">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="12" t="s">
+      <c r="I11" s="27"/>
+      <c r="J11" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="J11" s="13" t="s">
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+    </row>
+    <row r="12" spans="1:14" ht="30" customHeight="1">
+      <c r="A12" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-    </row>
-    <row r="12" spans="1:14" ht="30" customHeight="1">
-      <c r="A12" s="16" t="s">
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="13" t="s">
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="17" t="s">
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+    </row>
+    <row r="13" spans="1:14" ht="4.5" customHeight="1">
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+    </row>
+    <row r="14" spans="1:14" ht="28.5" customHeight="1">
+      <c r="A14" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="17"/>
-    </row>
-    <row r="13" spans="1:14" ht="4.5" customHeight="1">
-      <c r="A13" s="18"/>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="18"/>
-      <c r="N13" s="18"/>
-    </row>
-    <row r="14" spans="1:14" ht="28.5" customHeight="1">
-      <c r="A14" s="19" t="s">
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="20"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
     </row>
     <row r="15" spans="1:14" ht="30" customHeight="1">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
+      <c r="A15" s="23"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
     </row>
     <row r="16" spans="1:14" ht="4.5" customHeight="1">
-      <c r="A16" s="21"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="21"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="21"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="21"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
     </row>
     <row r="17" spans="1:14" ht="33" customHeight="1">
       <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22" t="s">
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="J17" s="22" t="s">
+      <c r="K17" s="26"/>
+      <c r="L17" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22" t="s">
+      <c r="M17" s="26"/>
+      <c r="N17" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="M17" s="22"/>
-      <c r="N17" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="24.75" customHeight="1">
       <c r="A18" s="4">
         <v>1</v>
       </c>
-      <c r="B18" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="24" t="s">
-        <v>32</v>
-      </c>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
+      <c r="B18" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
       <c r="I18" s="5">
         <v>1</v>
       </c>
-      <c r="J18" s="25">
+      <c r="J18" s="13">
         <v>9625000</v>
       </c>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25">
+      <c r="K18" s="13"/>
+      <c r="L18" s="13">
         <v>9625000</v>
       </c>
-      <c r="M18" s="25"/>
+      <c r="M18" s="13"/>
       <c r="N18" s="6">
         <v>962500</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="24.75" customHeight="1">
       <c r="A19" s="4"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="23"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
       <c r="I19" s="5"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+      <c r="L19" s="13"/>
+      <c r="M19" s="13"/>
       <c r="N19" s="6"/>
     </row>
     <row r="20" spans="1:14" ht="24.75" customHeight="1">
       <c r="A20" s="4"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
       <c r="I20" s="5"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="13"/>
       <c r="N20" s="6"/>
     </row>
     <row r="21" spans="1:14" ht="24.75" customHeight="1">
       <c r="A21" s="4"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="23"/>
-      <c r="H21" s="23"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
       <c r="I21" s="5"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
       <c r="N21" s="6"/>
     </row>
     <row r="22" spans="1:14" ht="24.75" customHeight="1">
       <c r="A22" s="4"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
       <c r="I22" s="5"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
+      <c r="J22" s="13"/>
+      <c r="K22" s="13"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="13"/>
       <c r="N22" s="6"/>
     </row>
     <row r="23" spans="1:14" ht="24.75" customHeight="1">
       <c r="A23" s="4"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
       <c r="I23" s="5"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+      <c r="L23" s="13"/>
+      <c r="M23" s="13"/>
       <c r="N23" s="6"/>
     </row>
     <row r="24" spans="1:14" ht="24.75" customHeight="1">
       <c r="A24" s="4"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
       <c r="I24" s="5"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="13"/>
       <c r="N24" s="6"/>
     </row>
     <row r="25" spans="1:14" ht="24.75" customHeight="1">
       <c r="A25" s="4"/>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
       <c r="I25" s="5"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
       <c r="N25" s="6"/>
     </row>
     <row r="26" spans="1:14" ht="24.75" customHeight="1">
       <c r="A26" s="4"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
       <c r="I26" s="5"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="25"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="25"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
+      <c r="M26" s="13"/>
       <c r="N26" s="6"/>
     </row>
     <row r="27" spans="1:14" ht="24.75" customHeight="1">
       <c r="A27" s="4"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
       <c r="I27" s="5"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="25"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
       <c r="N27" s="6"/>
     </row>
     <row r="28" spans="1:14" ht="24.75" customHeight="1">
       <c r="A28" s="4"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
       <c r="I28" s="5"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="25"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="13"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
       <c r="N28" s="6"/>
     </row>
     <row r="29" spans="1:14" ht="24.75" customHeight="1">
       <c r="A29" s="4"/>
-      <c r="B29" s="23"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="23"/>
-      <c r="H29" s="23"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
       <c r="I29" s="5"/>
-      <c r="J29" s="25"/>
-      <c r="K29" s="25"/>
-      <c r="L29" s="25"/>
-      <c r="M29" s="25"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
       <c r="N29" s="6"/>
     </row>
     <row r="30" spans="1:14" ht="24.75" customHeight="1">
       <c r="A30" s="4"/>
-      <c r="B30" s="23"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
-      <c r="F30" s="23"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="23"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
       <c r="I30" s="5"/>
-      <c r="J30" s="25"/>
-      <c r="K30" s="25"/>
-      <c r="L30" s="25"/>
-      <c r="M30" s="25"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
       <c r="N30" s="6"/>
     </row>
     <row r="31" spans="1:14" ht="24.75" customHeight="1">
       <c r="A31" s="4"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
       <c r="I31" s="5"/>
-      <c r="J31" s="25"/>
-      <c r="K31" s="25"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="25"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
       <c r="N31" s="6"/>
     </row>
     <row r="32" spans="1:14" ht="24.75" customHeight="1">
       <c r="A32" s="4"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="23"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="23"/>
-      <c r="H32" s="23"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
       <c r="I32" s="5"/>
-      <c r="J32" s="25"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="25"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
       <c r="N32" s="6"/>
     </row>
     <row r="33" spans="1:14" ht="24.75" customHeight="1">
       <c r="A33" s="4"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="23"/>
-      <c r="H33" s="23"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
       <c r="I33" s="5"/>
-      <c r="J33" s="25"/>
-      <c r="K33" s="25"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="25"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
       <c r="N33" s="6"/>
     </row>
     <row r="34" spans="1:14" ht="4.5" customHeight="1"/>
     <row r="35" spans="1:14" ht="33.75" customHeight="1">
-      <c r="A35" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="B35" s="28"/>
+      <c r="A35" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="14"/>
       <c r="C35" s="8">
         <v>1</v>
       </c>
       <c r="D35" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E35" s="15">
+        <v>9625000</v>
+      </c>
+      <c r="F35" s="15"/>
+      <c r="G35" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="29">
-        <v>9625000</v>
-      </c>
-      <c r="F35" s="29"/>
-      <c r="G35" s="7" t="s">
+      <c r="H35" s="16">
+        <v>962500</v>
+      </c>
+      <c r="I35" s="16"/>
+      <c r="J35" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H35" s="30">
-        <v>962500</v>
-      </c>
-      <c r="I35" s="30"/>
-      <c r="J35" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="K35" s="29">
+      <c r="K35" s="15">
         <v>10587500</v>
       </c>
-      <c r="L35" s="29"/>
-      <c r="M35" s="29"/>
-      <c r="N35" s="29"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="15"/>
     </row>
     <row r="36" spans="1:14" ht="4.5" customHeight="1"/>
     <row r="37" spans="1:14" ht="189.75" customHeight="1">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="14"/>
+      <c r="C37" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D37" s="31"/>
-      <c r="E37" s="31"/>
-      <c r="F37" s="31"/>
-      <c r="G37" s="31"/>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="31"/>
-      <c r="L37" s="31"/>
-      <c r="M37" s="31"/>
-      <c r="N37" s="31"/>
+      <c r="D37" s="17"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" ht="4.5" customHeight="1"/>
     <row r="39" spans="1:14" ht="16">
-      <c r="A39" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="26"/>
-      <c r="L39" s="26"/>
-      <c r="M39" s="26"/>
-      <c r="N39" s="26"/>
+      <c r="A39" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="10"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
+      <c r="J39" s="10"/>
+      <c r="K39" s="10"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
     </row>
     <row r="40" spans="1:14" ht="91.5" customHeight="1">
-      <c r="A40" s="27"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="106">
+    <mergeCell ref="J2:N2"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="H6:N7"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:N8"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:N9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="J10:N10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:N11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="H12:N12"/>
+    <mergeCell ref="A13:N13"/>
+    <mergeCell ref="A14:G15"/>
+    <mergeCell ref="H14:N15"/>
+    <mergeCell ref="A16:N16"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="L32:M32"/>
     <mergeCell ref="A39:N39"/>
     <mergeCell ref="A40:N40"/>
     <mergeCell ref="B33:E33"/>
@@ -1604,100 +1703,6 @@
     <mergeCell ref="K35:N35"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="C37:N37"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="B27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:G12"/>
-    <mergeCell ref="H12:N12"/>
-    <mergeCell ref="A13:N13"/>
-    <mergeCell ref="A14:G15"/>
-    <mergeCell ref="H14:N15"/>
-    <mergeCell ref="A16:N16"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:G9"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="J9:N9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="J10:N10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:N11"/>
-    <mergeCell ref="J2:N2"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="H6:N7"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:N8"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
